--- a/api/dataset/Ketahanan Pangan/hasil_ketahanan.xlsx
+++ b/api/dataset/Ketahanan Pangan/hasil_ketahanan.xlsx
@@ -1,26 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PENS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT\project_agridash\api\dataset\Ketahanan Pangan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{001AE546-51EA-4C24-BE83-75FCD886C6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B2BF6C-9326-478B-87C7-81E31BE1B568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B166D1E3-89D9-4EE0-B99C-949EC22EF1F8}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{B166D1E3-89D9-4EE0-B99C-949EC22EF1F8}"/>
   </bookViews>
   <sheets>
     <sheet name="hasil_ketahanan" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="59">
   <si>
     <t>Year</t>
   </si>
@@ -680,53 +691,54 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Aksen1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Aksen2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Aksen3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Aksen4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Aksen5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Aksen6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Aksen1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Aksen2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Aksen3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Aksen4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Aksen5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Aksen6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Aksen1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Aksen2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Aksen3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Aksen4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Aksen5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Aksen6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Aksen1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Aksen2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Aksen3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Aksen4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Aksen5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Aksen6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Baik" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Buruk" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Catatan" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Judul" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Judul 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Judul 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Judul 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Judul 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Keluaran" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Masukan" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Netral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Perhitungan" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Sel Periksa" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Sel Tertaut" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Teks Penjelasan" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Teks Peringatan" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1058,10 +1070,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{454119AF-1C0E-4683-B03E-0C86D8713EF4}">
-  <dimension ref="A1:U206"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:U305"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="17" max="17" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1126,7 +1141,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2018</v>
       </c>
@@ -1191,7 +1206,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2018</v>
       </c>
@@ -1256,7 +1271,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2018</v>
       </c>
@@ -1321,7 +1336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2018</v>
       </c>
@@ -1386,7 +1401,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2018</v>
       </c>
@@ -1451,7 +1466,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2018</v>
       </c>
@@ -1516,7 +1531,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2018</v>
       </c>
@@ -1581,7 +1596,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2018</v>
       </c>
@@ -1646,7 +1661,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2018</v>
       </c>
@@ -1711,7 +1726,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2018</v>
       </c>
@@ -1776,7 +1791,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2018</v>
       </c>
@@ -1841,7 +1856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2018</v>
       </c>
@@ -1906,7 +1921,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2018</v>
       </c>
@@ -1971,7 +1986,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2018</v>
       </c>
@@ -2036,7 +2051,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2018</v>
       </c>
@@ -2101,7 +2116,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2018</v>
       </c>
@@ -2166,7 +2181,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2018</v>
       </c>
@@ -2231,7 +2246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2018</v>
       </c>
@@ -2296,7 +2311,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2018</v>
       </c>
@@ -2361,7 +2376,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2018</v>
       </c>
@@ -2426,7 +2441,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2018</v>
       </c>
@@ -2491,7 +2506,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2018</v>
       </c>
@@ -2556,7 +2571,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2018</v>
       </c>
@@ -2621,7 +2636,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2018</v>
       </c>
@@ -2686,7 +2701,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2018</v>
       </c>
@@ -2751,7 +2766,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2018</v>
       </c>
@@ -2816,7 +2831,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2018</v>
       </c>
@@ -2881,7 +2896,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2018</v>
       </c>
@@ -2946,7 +2961,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2018</v>
       </c>
@@ -3011,7 +3026,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2018</v>
       </c>
@@ -3076,7 +3091,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2018</v>
       </c>
@@ -3141,7 +3156,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2018</v>
       </c>
@@ -3206,7 +3221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2018</v>
       </c>
@@ -3271,7 +3286,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2018</v>
       </c>
@@ -3336,7 +3351,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2018</v>
       </c>
@@ -3401,7 +3416,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2018</v>
       </c>
@@ -3466,7 +3481,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2018</v>
       </c>
@@ -3531,7 +3546,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2018</v>
       </c>
@@ -3596,7 +3611,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2019</v>
       </c>
@@ -3661,7 +3676,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2019</v>
       </c>
@@ -3726,7 +3741,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2019</v>
       </c>
@@ -3791,7 +3806,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2019</v>
       </c>
@@ -3856,7 +3871,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2019</v>
       </c>
@@ -3921,7 +3936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2019</v>
       </c>
@@ -3986,7 +4001,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2019</v>
       </c>
@@ -4051,7 +4066,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2019</v>
       </c>
@@ -4116,7 +4131,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2019</v>
       </c>
@@ -4181,7 +4196,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2019</v>
       </c>
@@ -4246,7 +4261,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2019</v>
       </c>
@@ -4311,7 +4326,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2019</v>
       </c>
@@ -4376,7 +4391,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2019</v>
       </c>
@@ -4441,7 +4456,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2019</v>
       </c>
@@ -4506,7 +4521,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2019</v>
       </c>
@@ -4571,7 +4586,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2019</v>
       </c>
@@ -4636,7 +4651,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2019</v>
       </c>
@@ -4701,7 +4716,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2019</v>
       </c>
@@ -4766,7 +4781,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2019</v>
       </c>
@@ -4831,7 +4846,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2019</v>
       </c>
@@ -4896,7 +4911,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2019</v>
       </c>
@@ -4961,7 +4976,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2019</v>
       </c>
@@ -5026,7 +5041,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2019</v>
       </c>
@@ -5091,7 +5106,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2019</v>
       </c>
@@ -5156,7 +5171,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>2019</v>
       </c>
@@ -5221,7 +5236,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>2019</v>
       </c>
@@ -5286,7 +5301,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>2019</v>
       </c>
@@ -5351,7 +5366,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>2019</v>
       </c>
@@ -5416,7 +5431,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>2019</v>
       </c>
@@ -5481,7 +5496,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>2019</v>
       </c>
@@ -5546,7 +5561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>2019</v>
       </c>
@@ -5611,7 +5626,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>2019</v>
       </c>
@@ -5676,7 +5691,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>2019</v>
       </c>
@@ -5741,7 +5756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>2019</v>
       </c>
@@ -5806,7 +5821,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>2019</v>
       </c>
@@ -5871,7 +5886,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>2019</v>
       </c>
@@ -5936,7 +5951,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>2019</v>
       </c>
@@ -6001,7 +6016,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>2019</v>
       </c>
@@ -6066,7 +6081,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>2020</v>
       </c>
@@ -6131,7 +6146,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>2020</v>
       </c>
@@ -6196,7 +6211,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>2020</v>
       </c>
@@ -6261,7 +6276,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>2020</v>
       </c>
@@ -6326,7 +6341,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>2020</v>
       </c>
@@ -6391,7 +6406,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>2020</v>
       </c>
@@ -6456,7 +6471,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>2020</v>
       </c>
@@ -6521,7 +6536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>2020</v>
       </c>
@@ -6586,7 +6601,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>2020</v>
       </c>
@@ -6651,7 +6666,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>2020</v>
       </c>
@@ -6716,7 +6731,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>2020</v>
       </c>
@@ -6781,7 +6796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>2020</v>
       </c>
@@ -6846,7 +6861,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>2020</v>
       </c>
@@ -6911,7 +6926,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>2020</v>
       </c>
@@ -6976,7 +6991,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>2020</v>
       </c>
@@ -7041,7 +7056,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>2020</v>
       </c>
@@ -7106,7 +7121,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>2020</v>
       </c>
@@ -7171,7 +7186,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>2020</v>
       </c>
@@ -7236,7 +7251,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>2020</v>
       </c>
@@ -7301,7 +7316,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>2020</v>
       </c>
@@ -7366,7 +7381,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>2020</v>
       </c>
@@ -7431,7 +7446,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>2020</v>
       </c>
@@ -7496,7 +7511,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>2020</v>
       </c>
@@ -7561,7 +7576,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>2020</v>
       </c>
@@ -7626,7 +7641,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>2020</v>
       </c>
@@ -7691,7 +7706,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>2020</v>
       </c>
@@ -7756,7 +7771,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>2020</v>
       </c>
@@ -7821,7 +7836,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>2020</v>
       </c>
@@ -7886,7 +7901,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>2020</v>
       </c>
@@ -7951,7 +7966,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>2020</v>
       </c>
@@ -8016,7 +8031,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>2020</v>
       </c>
@@ -8081,7 +8096,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>2020</v>
       </c>
@@ -8146,7 +8161,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>2020</v>
       </c>
@@ -8211,7 +8226,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>2020</v>
       </c>
@@ -8276,7 +8291,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>2020</v>
       </c>
@@ -8341,7 +8356,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>2020</v>
       </c>
@@ -8406,7 +8421,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>2020</v>
       </c>
@@ -8471,7 +8486,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>2020</v>
       </c>
@@ -8536,7 +8551,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>2021</v>
       </c>
@@ -8601,7 +8616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>2021</v>
       </c>
@@ -8666,7 +8681,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>2021</v>
       </c>
@@ -8731,7 +8746,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>2021</v>
       </c>
@@ -8796,7 +8811,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>2021</v>
       </c>
@@ -8861,7 +8876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>2021</v>
       </c>
@@ -8926,7 +8941,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>2021</v>
       </c>
@@ -8991,7 +9006,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>2021</v>
       </c>
@@ -9056,7 +9071,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>2021</v>
       </c>
@@ -9121,7 +9136,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>2021</v>
       </c>
@@ -9186,7 +9201,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>2021</v>
       </c>
@@ -9251,7 +9266,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>2021</v>
       </c>
@@ -9316,7 +9331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>2021</v>
       </c>
@@ -9381,7 +9396,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>2021</v>
       </c>
@@ -9446,7 +9461,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>2021</v>
       </c>
@@ -9511,7 +9526,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>2021</v>
       </c>
@@ -9576,7 +9591,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>2021</v>
       </c>
@@ -9641,7 +9656,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>2021</v>
       </c>
@@ -9706,7 +9721,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>2021</v>
       </c>
@@ -9771,7 +9786,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2021</v>
       </c>
@@ -9836,7 +9851,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>2021</v>
       </c>
@@ -9901,7 +9916,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>2021</v>
       </c>
@@ -9966,7 +9981,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>2021</v>
       </c>
@@ -10031,7 +10046,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>2021</v>
       </c>
@@ -10096,7 +10111,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="140" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>2021</v>
       </c>
@@ -10161,7 +10176,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="141" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>2021</v>
       </c>
@@ -10226,7 +10241,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="142" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>2021</v>
       </c>
@@ -10291,7 +10306,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>2021</v>
       </c>
@@ -10356,7 +10371,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2021</v>
       </c>
@@ -10421,7 +10436,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2021</v>
       </c>
@@ -10486,7 +10501,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>2021</v>
       </c>
@@ -10551,7 +10566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2021</v>
       </c>
@@ -10616,7 +10631,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="148" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>2021</v>
       </c>
@@ -10681,7 +10696,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>2021</v>
       </c>
@@ -10746,7 +10761,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>2021</v>
       </c>
@@ -10811,7 +10826,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2021</v>
       </c>
@@ -10876,7 +10891,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="152" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2021</v>
       </c>
@@ -10941,7 +10956,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2021</v>
       </c>
@@ -11006,7 +11021,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="154" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2022</v>
       </c>
@@ -11071,7 +11086,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="155" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>2022</v>
       </c>
@@ -11136,7 +11151,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="156" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>2022</v>
       </c>
@@ -11201,7 +11216,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>2022</v>
       </c>
@@ -11266,7 +11281,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>2022</v>
       </c>
@@ -11331,7 +11346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2022</v>
       </c>
@@ -11396,7 +11411,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="160" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>2022</v>
       </c>
@@ -11461,7 +11476,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="161" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2022</v>
       </c>
@@ -11526,7 +11541,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="162" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>2022</v>
       </c>
@@ -11591,7 +11606,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="163" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2022</v>
       </c>
@@ -11656,7 +11671,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>2022</v>
       </c>
@@ -11721,7 +11736,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="165" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>2022</v>
       </c>
@@ -11786,7 +11801,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="166" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>2022</v>
       </c>
@@ -11851,7 +11866,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="167" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>2022</v>
       </c>
@@ -11916,7 +11931,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="168" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>2022</v>
       </c>
@@ -11981,7 +11996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="169" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2022</v>
       </c>
@@ -12046,7 +12061,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="170" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>2022</v>
       </c>
@@ -12111,7 +12126,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="171" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2022</v>
       </c>
@@ -12176,7 +12191,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="172" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>2022</v>
       </c>
@@ -12241,7 +12256,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="173" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>2022</v>
       </c>
@@ -12306,7 +12321,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>2022</v>
       </c>
@@ -12371,7 +12386,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="175" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>2022</v>
       </c>
@@ -12436,7 +12451,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="176" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>2022</v>
       </c>
@@ -12501,7 +12516,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>2022</v>
       </c>
@@ -12566,7 +12581,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>2022</v>
       </c>
@@ -12631,7 +12646,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="179" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>2022</v>
       </c>
@@ -12696,7 +12711,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="180" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>2022</v>
       </c>
@@ -12761,7 +12776,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="181" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>2022</v>
       </c>
@@ -12826,7 +12841,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>2022</v>
       </c>
@@ -12891,7 +12906,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="183" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>2022</v>
       </c>
@@ -12956,7 +12971,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="184" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>2022</v>
       </c>
@@ -13021,7 +13036,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="185" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>2022</v>
       </c>
@@ -13086,7 +13101,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>2022</v>
       </c>
@@ -13151,7 +13166,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="187" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>2022</v>
       </c>
@@ -13216,7 +13231,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="188" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>2022</v>
       </c>
@@ -13281,7 +13296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="189" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>2022</v>
       </c>
@@ -13346,7 +13361,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="190" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>2022</v>
       </c>
@@ -13411,7 +13426,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="191" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>2022</v>
       </c>
@@ -13476,7 +13491,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="192" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>2023</v>
       </c>
@@ -13541,7 +13556,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>2023</v>
       </c>
@@ -13606,7 +13621,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="194" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>2023</v>
       </c>
@@ -13671,7 +13686,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="195" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>2023</v>
       </c>
@@ -13736,7 +13751,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>2023</v>
       </c>
@@ -13801,654 +13816,2337 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B197" t="s">
-        <v>21</v>
-      </c>
-      <c r="C197">
-        <v>201139.46849999999</v>
-      </c>
-      <c r="D197">
-        <v>102423.2208</v>
-      </c>
-      <c r="E197">
-        <v>6741.7920000000004</v>
-      </c>
-      <c r="F197">
-        <v>20966.140800000001</v>
-      </c>
-      <c r="G197">
-        <v>42</v>
-      </c>
-      <c r="H197">
-        <v>23</v>
-      </c>
-      <c r="I197">
-        <v>263</v>
-      </c>
-      <c r="J197">
+        <v>26</v>
+      </c>
+      <c r="Q197" s="2">
+        <v>85.726256869736133</v>
+      </c>
+      <c r="R197">
+        <v>5</v>
+      </c>
+      <c r="T197">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="198" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>2023</v>
+      </c>
+      <c r="B198" t="s">
         <v>27</v>
       </c>
-      <c r="K197">
-        <v>859399.85250000004</v>
-      </c>
-      <c r="L197">
-        <v>66.05</v>
-      </c>
-      <c r="M197">
-        <v>2537432.415</v>
-      </c>
-      <c r="N197">
-        <v>7.65</v>
-      </c>
-      <c r="O197">
-        <v>18.440000000000001</v>
-      </c>
-      <c r="P197">
-        <v>27710.587800000001</v>
-      </c>
-      <c r="Q197">
-        <v>72.59</v>
-      </c>
-      <c r="R197">
-        <v>6</v>
-      </c>
-      <c r="S197">
-        <v>6</v>
-      </c>
-      <c r="T197">
-        <v>4</v>
-      </c>
-      <c r="U197">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="198" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A198">
-        <v>2024</v>
-      </c>
-      <c r="B198" t="s">
-        <v>22</v>
-      </c>
-      <c r="C198">
-        <v>481273.23629999999</v>
-      </c>
-      <c r="D198">
-        <v>240658.04519999999</v>
-      </c>
-      <c r="E198">
-        <v>25213.053599999999</v>
-      </c>
-      <c r="F198">
-        <v>10338.4548</v>
-      </c>
-      <c r="G198">
-        <v>98</v>
-      </c>
-      <c r="H198">
-        <v>47</v>
-      </c>
-      <c r="I198">
-        <v>133</v>
-      </c>
-      <c r="J198">
-        <v>87</v>
-      </c>
-      <c r="K198">
-        <v>1206374.243</v>
-      </c>
-      <c r="L198">
-        <v>72.94</v>
-      </c>
-      <c r="M198">
-        <v>2162550.443</v>
-      </c>
-      <c r="N198">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="O198">
-        <v>6.51</v>
-      </c>
-      <c r="P198">
-        <v>59339.218500000003</v>
-      </c>
-      <c r="Q198">
-        <v>85.82</v>
+      <c r="Q198" s="2">
+        <v>78.548371445181104</v>
       </c>
       <c r="R198">
         <v>5</v>
       </c>
-      <c r="S198">
-        <v>5</v>
-      </c>
       <c r="T198">
         <v>5</v>
       </c>
-      <c r="U198">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="199" spans="1:21" x14ac:dyDescent="0.35">
+    </row>
+    <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B199" t="s">
-        <v>23</v>
-      </c>
-      <c r="C199">
-        <v>226356.67559999999</v>
-      </c>
-      <c r="D199">
-        <v>300477.924</v>
-      </c>
-      <c r="E199">
-        <v>5925.0780000000004</v>
-      </c>
-      <c r="F199">
-        <v>79289.924400000004</v>
-      </c>
-      <c r="G199">
-        <v>101</v>
-      </c>
-      <c r="H199">
-        <v>16</v>
-      </c>
-      <c r="I199">
-        <v>248</v>
-      </c>
-      <c r="J199">
-        <v>84</v>
-      </c>
-      <c r="K199">
-        <v>1042135.92</v>
-      </c>
-      <c r="L199">
-        <v>72.86</v>
-      </c>
-      <c r="M199">
-        <v>2061695.9480000001</v>
-      </c>
-      <c r="N199">
-        <v>5.05</v>
-      </c>
-      <c r="O199">
-        <v>7.71</v>
-      </c>
-      <c r="P199">
-        <v>36696.3266</v>
-      </c>
-      <c r="Q199">
-        <v>86.34</v>
+        <v>28</v>
+      </c>
+      <c r="Q199" s="2">
+        <v>84.94676653774566</v>
       </c>
       <c r="R199">
-        <v>6</v>
-      </c>
-      <c r="S199">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T199">
-        <v>6</v>
-      </c>
-      <c r="U199">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="200" spans="1:21" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B200" t="s">
-        <v>24</v>
-      </c>
-      <c r="C200">
-        <v>744092.87309999997</v>
-      </c>
-      <c r="D200">
-        <v>249011.41680000001</v>
-      </c>
-      <c r="E200">
-        <v>2494.8791999999999</v>
-      </c>
-      <c r="F200">
-        <v>24912.378000000001</v>
-      </c>
-      <c r="G200">
-        <v>70</v>
-      </c>
-      <c r="H200">
-        <v>25</v>
-      </c>
-      <c r="I200">
-        <v>368</v>
-      </c>
-      <c r="J200">
-        <v>74</v>
-      </c>
-      <c r="K200">
-        <v>1016731.013</v>
-      </c>
-      <c r="L200">
-        <v>71.126000000000005</v>
-      </c>
-      <c r="M200">
-        <v>2473581.5180000002</v>
-      </c>
-      <c r="N200">
-        <v>4.29</v>
-      </c>
-      <c r="O200">
-        <v>11.29</v>
-      </c>
-      <c r="P200">
-        <v>84349.243100000007</v>
-      </c>
-      <c r="Q200">
-        <v>85.55</v>
+        <v>29</v>
+      </c>
+      <c r="Q200" s="2">
+        <v>77.976000043511405</v>
       </c>
       <c r="R200">
-        <v>6</v>
-      </c>
-      <c r="S200">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T200">
-        <v>6</v>
-      </c>
-      <c r="U200">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="201" spans="1:21" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B201" t="s">
-        <v>25</v>
-      </c>
-      <c r="C201">
-        <v>256341.33410000001</v>
-      </c>
-      <c r="D201">
-        <v>219237.39</v>
-      </c>
-      <c r="E201">
-        <v>4436.2655999999997</v>
-      </c>
-      <c r="F201">
-        <v>47767.885199999997</v>
-      </c>
-      <c r="G201">
-        <v>50</v>
-      </c>
-      <c r="H201">
-        <v>15</v>
-      </c>
-      <c r="I201">
-        <v>171</v>
-      </c>
-      <c r="J201">
-        <v>71</v>
-      </c>
-      <c r="K201">
-        <v>1013759.303</v>
-      </c>
-      <c r="L201">
-        <v>68.31</v>
-      </c>
-      <c r="M201">
-        <v>1848074.76</v>
-      </c>
-      <c r="N201">
-        <v>3.92</v>
-      </c>
-      <c r="O201">
-        <v>12.47</v>
-      </c>
-      <c r="P201">
-        <v>32211.279500000001</v>
-      </c>
-      <c r="Q201">
-        <v>75.78</v>
+        <v>30</v>
+      </c>
+      <c r="Q201" s="2">
+        <v>80.294361239199915</v>
       </c>
       <c r="R201">
-        <v>4</v>
-      </c>
-      <c r="S201">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T201">
-        <v>4</v>
-      </c>
-      <c r="U201">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="202" spans="1:21" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B202" t="s">
-        <v>21</v>
-      </c>
-      <c r="C202">
-        <v>205162.25889999999</v>
-      </c>
-      <c r="D202">
-        <v>104471.6853</v>
-      </c>
-      <c r="E202">
-        <v>6876.6278000000002</v>
-      </c>
-      <c r="F202">
-        <v>21385.463599999999</v>
-      </c>
-      <c r="G202">
-        <v>42</v>
-      </c>
-      <c r="H202">
-        <v>23</v>
-      </c>
-      <c r="I202">
-        <v>263</v>
-      </c>
-      <c r="J202">
-        <v>27</v>
-      </c>
-      <c r="K202">
-        <v>902369.84510000004</v>
-      </c>
-      <c r="L202">
-        <v>66.55</v>
-      </c>
-      <c r="M202">
-        <v>2664304.0359999998</v>
-      </c>
-      <c r="N202">
-        <v>7.45</v>
-      </c>
-      <c r="O202">
-        <v>17.940000000000001</v>
-      </c>
-      <c r="P202">
-        <v>29096.117200000001</v>
-      </c>
-      <c r="Q202">
-        <v>73.59</v>
+        <v>31</v>
+      </c>
+      <c r="Q202" s="2">
+        <v>73.643659412560552</v>
       </c>
       <c r="R202">
         <v>4</v>
       </c>
-      <c r="S202">
-        <v>4</v>
-      </c>
       <c r="T202">
         <v>4</v>
       </c>
-      <c r="U202">
+    </row>
+    <row r="203" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>2023</v>
+      </c>
+      <c r="B203" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q203" s="2">
+        <v>72.38478810004618</v>
+      </c>
+      <c r="R203">
         <v>4</v>
       </c>
-    </row>
-    <row r="203" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A203">
+      <c r="T203">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>2023</v>
+      </c>
+      <c r="B204" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q204" s="2">
+        <v>84.692101353827155</v>
+      </c>
+      <c r="R204">
+        <v>5</v>
+      </c>
+      <c r="T204">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="205" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>2023</v>
+      </c>
+      <c r="B205" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q205" s="2">
+        <v>78.161069955578299</v>
+      </c>
+      <c r="R205">
+        <v>5</v>
+      </c>
+      <c r="T205">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="206" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>2023</v>
+      </c>
+      <c r="B206" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q206" s="2">
+        <v>82.20623492820144</v>
+      </c>
+      <c r="R206">
+        <v>5</v>
+      </c>
+      <c r="T206">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="207" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>2023</v>
+      </c>
+      <c r="B207" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q207" s="2">
+        <v>72.392534416137522</v>
+      </c>
+      <c r="R207">
+        <v>4</v>
+      </c>
+      <c r="T207">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>2023</v>
+      </c>
+      <c r="B208" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q208" s="2">
+        <v>74.533931523200934</v>
+      </c>
+      <c r="R208">
+        <v>4</v>
+      </c>
+      <c r="T208">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>2023</v>
+      </c>
+      <c r="B209" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q209" s="2">
+        <v>78.66200013664961</v>
+      </c>
+      <c r="R209">
+        <v>5</v>
+      </c>
+      <c r="T209">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="210" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>2023</v>
+      </c>
+      <c r="B210" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q210" s="2">
+        <v>86.465155149985989</v>
+      </c>
+      <c r="R210">
+        <v>5</v>
+      </c>
+      <c r="T210">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="211" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>2023</v>
+      </c>
+      <c r="B211" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q211" s="2">
+        <v>80.141161876374852</v>
+      </c>
+      <c r="R211">
+        <v>5</v>
+      </c>
+      <c r="T211">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>2023</v>
+      </c>
+      <c r="B212" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q212" s="2">
+        <v>83.35558698767538</v>
+      </c>
+      <c r="R212">
+        <v>5</v>
+      </c>
+      <c r="T212">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>2023</v>
+      </c>
+      <c r="B213" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q213" s="2">
+        <v>85.776000026184335</v>
+      </c>
+      <c r="R213">
+        <v>5</v>
+      </c>
+      <c r="T213">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>2023</v>
+      </c>
+      <c r="B214" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q214" s="2">
+        <v>80.796483285573785</v>
+      </c>
+      <c r="R214">
+        <v>5</v>
+      </c>
+      <c r="T214">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="215" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>2023</v>
+      </c>
+      <c r="B215" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q215" s="2">
+        <v>85.589100755718221</v>
+      </c>
+      <c r="R215">
+        <v>5</v>
+      </c>
+      <c r="T215">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>2023</v>
+      </c>
+      <c r="B216" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q216" s="2">
+        <v>82.153599055853107</v>
+      </c>
+      <c r="R216">
+        <v>5</v>
+      </c>
+      <c r="T216">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>2023</v>
+      </c>
+      <c r="B217" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q217" s="2">
+        <v>85.977601649026695</v>
+      </c>
+      <c r="R217">
+        <v>5</v>
+      </c>
+      <c r="T217">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="218" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>2023</v>
+      </c>
+      <c r="B218" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q218" s="2">
+        <v>76.322000034332291</v>
+      </c>
+      <c r="R218">
+        <v>5</v>
+      </c>
+      <c r="T218">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>2023</v>
+      </c>
+      <c r="B219" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q219" s="2">
+        <v>75.930888395951413</v>
+      </c>
+      <c r="R219">
+        <v>5</v>
+      </c>
+      <c r="T219">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>2023</v>
+      </c>
+      <c r="B220" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q220" s="2">
+        <v>77.575470991577305</v>
+      </c>
+      <c r="R220">
+        <v>5</v>
+      </c>
+      <c r="T220">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="221" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>2023</v>
+      </c>
+      <c r="B221" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q221" s="2">
+        <v>87.004658972659954</v>
+      </c>
+      <c r="R221">
+        <v>6</v>
+      </c>
+      <c r="T221">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="222" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>2023</v>
+      </c>
+      <c r="B222" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q222" s="2">
+        <v>72.371720114018089</v>
+      </c>
+      <c r="R222">
+        <v>4</v>
+      </c>
+      <c r="T222">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>2023</v>
+      </c>
+      <c r="B223" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q223" s="2">
+        <v>73.919521221486264</v>
+      </c>
+      <c r="R223">
+        <v>4</v>
+      </c>
+      <c r="T223">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>2023</v>
+      </c>
+      <c r="B224" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q224" s="2">
+        <v>86.293780909304843</v>
+      </c>
+      <c r="R224">
+        <v>5</v>
+      </c>
+      <c r="T224">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="225" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>2023</v>
+      </c>
+      <c r="B225" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q225" s="2">
+        <v>78.142126965073672</v>
+      </c>
+      <c r="R225">
+        <v>5</v>
+      </c>
+      <c r="T225">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="226" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>2023</v>
+      </c>
+      <c r="B226" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q226" s="2">
+        <v>72.282000066328052</v>
+      </c>
+      <c r="R226">
+        <v>4</v>
+      </c>
+      <c r="T226">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>2023</v>
+      </c>
+      <c r="B227" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q227" s="2">
+        <v>82.043763843430057</v>
+      </c>
+      <c r="R227">
+        <v>5</v>
+      </c>
+      <c r="T227">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="228" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>2023</v>
+      </c>
+      <c r="B228" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q228" s="2">
+        <v>84.39315035989604</v>
+      </c>
+      <c r="R228">
+        <v>5</v>
+      </c>
+      <c r="T228">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="229" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>2023</v>
+      </c>
+      <c r="B229" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q229" s="2">
+        <v>86.730469164002713</v>
+      </c>
+      <c r="R229">
+        <v>5</v>
+      </c>
+      <c r="T229">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="230" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>2024</v>
+      </c>
+      <c r="B230" t="s">
+        <v>21</v>
+      </c>
+      <c r="C230">
+        <v>201139.46849999999</v>
+      </c>
+      <c r="D230">
+        <v>102423.2208</v>
+      </c>
+      <c r="E230">
+        <v>6741.7920000000004</v>
+      </c>
+      <c r="F230">
+        <v>20966.140800000001</v>
+      </c>
+      <c r="G230">
+        <v>42</v>
+      </c>
+      <c r="H230">
+        <v>23</v>
+      </c>
+      <c r="I230">
+        <v>263</v>
+      </c>
+      <c r="J230">
+        <v>27</v>
+      </c>
+      <c r="K230">
+        <v>859399.85250000004</v>
+      </c>
+      <c r="L230">
+        <v>66.05</v>
+      </c>
+      <c r="M230">
+        <v>2537432.415</v>
+      </c>
+      <c r="N230">
+        <v>7.65</v>
+      </c>
+      <c r="O230">
+        <v>18.440000000000001</v>
+      </c>
+      <c r="P230">
+        <v>27710.587800000001</v>
+      </c>
+      <c r="Q230">
+        <v>72.59</v>
+      </c>
+      <c r="R230">
+        <v>6</v>
+      </c>
+      <c r="S230">
+        <v>6</v>
+      </c>
+      <c r="T230">
+        <v>4</v>
+      </c>
+      <c r="U230">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="231" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>2024</v>
+      </c>
+      <c r="B231" t="s">
+        <v>22</v>
+      </c>
+      <c r="C231">
+        <v>481273.23629999999</v>
+      </c>
+      <c r="D231">
+        <v>240658.04519999999</v>
+      </c>
+      <c r="E231">
+        <v>25213.053599999999</v>
+      </c>
+      <c r="F231">
+        <v>10338.4548</v>
+      </c>
+      <c r="G231">
+        <v>98</v>
+      </c>
+      <c r="H231">
+        <v>47</v>
+      </c>
+      <c r="I231">
+        <v>133</v>
+      </c>
+      <c r="J231">
+        <v>87</v>
+      </c>
+      <c r="K231">
+        <v>1206374.243</v>
+      </c>
+      <c r="L231">
+        <v>72.94</v>
+      </c>
+      <c r="M231">
+        <v>2162550.443</v>
+      </c>
+      <c r="N231">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="O231">
+        <v>6.51</v>
+      </c>
+      <c r="P231">
+        <v>59339.218500000003</v>
+      </c>
+      <c r="Q231">
+        <v>85.82</v>
+      </c>
+      <c r="R231">
+        <v>5</v>
+      </c>
+      <c r="S231">
+        <v>5</v>
+      </c>
+      <c r="T231">
+        <v>5</v>
+      </c>
+      <c r="U231">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="232" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>2024</v>
+      </c>
+      <c r="B232" t="s">
+        <v>23</v>
+      </c>
+      <c r="C232">
+        <v>226356.67559999999</v>
+      </c>
+      <c r="D232">
+        <v>300477.924</v>
+      </c>
+      <c r="E232">
+        <v>5925.0780000000004</v>
+      </c>
+      <c r="F232">
+        <v>79289.924400000004</v>
+      </c>
+      <c r="G232">
+        <v>101</v>
+      </c>
+      <c r="H232">
+        <v>16</v>
+      </c>
+      <c r="I232">
+        <v>248</v>
+      </c>
+      <c r="J232">
+        <v>84</v>
+      </c>
+      <c r="K232">
+        <v>1042135.92</v>
+      </c>
+      <c r="L232">
+        <v>72.86</v>
+      </c>
+      <c r="M232">
+        <v>2061695.9480000001</v>
+      </c>
+      <c r="N232">
+        <v>5.05</v>
+      </c>
+      <c r="O232">
+        <v>7.71</v>
+      </c>
+      <c r="P232">
+        <v>36696.3266</v>
+      </c>
+      <c r="Q232">
+        <v>86.34</v>
+      </c>
+      <c r="R232">
+        <v>6</v>
+      </c>
+      <c r="S232">
+        <v>6</v>
+      </c>
+      <c r="T232">
+        <v>6</v>
+      </c>
+      <c r="U232">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="233" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>2024</v>
+      </c>
+      <c r="B233" t="s">
+        <v>24</v>
+      </c>
+      <c r="C233">
+        <v>744092.87309999997</v>
+      </c>
+      <c r="D233">
+        <v>249011.41680000001</v>
+      </c>
+      <c r="E233">
+        <v>2494.8791999999999</v>
+      </c>
+      <c r="F233">
+        <v>24912.378000000001</v>
+      </c>
+      <c r="G233">
+        <v>70</v>
+      </c>
+      <c r="H233">
+        <v>25</v>
+      </c>
+      <c r="I233">
+        <v>368</v>
+      </c>
+      <c r="J233">
+        <v>74</v>
+      </c>
+      <c r="K233">
+        <v>1016731.013</v>
+      </c>
+      <c r="L233">
+        <v>71.126000000000005</v>
+      </c>
+      <c r="M233">
+        <v>2473581.5180000002</v>
+      </c>
+      <c r="N233">
+        <v>4.29</v>
+      </c>
+      <c r="O233">
+        <v>11.29</v>
+      </c>
+      <c r="P233">
+        <v>84349.243100000007</v>
+      </c>
+      <c r="Q233">
+        <v>85.55</v>
+      </c>
+      <c r="R233">
+        <v>6</v>
+      </c>
+      <c r="S233">
+        <v>6</v>
+      </c>
+      <c r="T233">
+        <v>6</v>
+      </c>
+      <c r="U233">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="234" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>2024</v>
+      </c>
+      <c r="B234" t="s">
+        <v>25</v>
+      </c>
+      <c r="C234">
+        <v>256341.33410000001</v>
+      </c>
+      <c r="D234">
+        <v>219237.39</v>
+      </c>
+      <c r="E234">
+        <v>4436.2655999999997</v>
+      </c>
+      <c r="F234">
+        <v>47767.885199999997</v>
+      </c>
+      <c r="G234">
+        <v>50</v>
+      </c>
+      <c r="H234">
+        <v>15</v>
+      </c>
+      <c r="I234">
+        <v>171</v>
+      </c>
+      <c r="J234">
+        <v>71</v>
+      </c>
+      <c r="K234">
+        <v>1013759.303</v>
+      </c>
+      <c r="L234">
+        <v>68.31</v>
+      </c>
+      <c r="M234">
+        <v>1848074.76</v>
+      </c>
+      <c r="N234">
+        <v>3.92</v>
+      </c>
+      <c r="O234">
+        <v>12.47</v>
+      </c>
+      <c r="P234">
+        <v>32211.279500000001</v>
+      </c>
+      <c r="Q234">
+        <v>75.78</v>
+      </c>
+      <c r="R234">
+        <v>4</v>
+      </c>
+      <c r="S234">
+        <v>4</v>
+      </c>
+      <c r="T234">
+        <v>4</v>
+      </c>
+      <c r="U234">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>2024</v>
+      </c>
+      <c r="B235" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q235" s="2">
+        <v>84.836590638611071</v>
+      </c>
+      <c r="R235">
+        <v>5</v>
+      </c>
+      <c r="T235">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="236" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>2024</v>
+      </c>
+      <c r="B236" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q236" s="2">
+        <v>78.976677548360499</v>
+      </c>
+      <c r="R236">
+        <v>5</v>
+      </c>
+      <c r="T236">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="237" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>2024</v>
+      </c>
+      <c r="B237" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q237" s="2">
+        <v>85.321903569494665</v>
+      </c>
+      <c r="R237">
+        <v>5</v>
+      </c>
+      <c r="T237">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="238" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>2024</v>
+      </c>
+      <c r="B238" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q238" s="2">
+        <v>77.02880006067754</v>
+      </c>
+      <c r="R238">
+        <v>5</v>
+      </c>
+      <c r="T238">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="239" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>2024</v>
+      </c>
+      <c r="B239" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q239" s="2">
+        <v>81.696273834972104</v>
+      </c>
+      <c r="R239">
+        <v>5</v>
+      </c>
+      <c r="T239">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="240" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>2024</v>
+      </c>
+      <c r="B240" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q240" s="2">
+        <v>74.701084821146466</v>
+      </c>
+      <c r="R240">
+        <v>4</v>
+      </c>
+      <c r="T240">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>2024</v>
+      </c>
+      <c r="B241" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q241" s="2">
+        <v>73.074259052250071</v>
+      </c>
+      <c r="R241">
+        <v>4</v>
+      </c>
+      <c r="T241">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>2024</v>
+      </c>
+      <c r="B242" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q242" s="2">
+        <v>84.995229627770684</v>
+      </c>
+      <c r="R242">
+        <v>5</v>
+      </c>
+      <c r="T242">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="243" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>2024</v>
+      </c>
+      <c r="B243" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q243" s="2">
+        <v>75.978108522675143</v>
+      </c>
+      <c r="R243">
+        <v>5</v>
+      </c>
+      <c r="T243">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="244" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>2024</v>
+      </c>
+      <c r="B244" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q244" s="2">
+        <v>82.721987700777859</v>
+      </c>
+      <c r="R244">
+        <v>5</v>
+      </c>
+      <c r="T244">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="245" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>2024</v>
+      </c>
+      <c r="B245" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q245" s="2">
+        <v>73.038792400402698</v>
+      </c>
+      <c r="R245">
+        <v>4</v>
+      </c>
+      <c r="T245">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>2024</v>
+      </c>
+      <c r="B246" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q246" s="2">
+        <v>74.967478390906919</v>
+      </c>
+      <c r="R246">
+        <v>4</v>
+      </c>
+      <c r="T246">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>2024</v>
+      </c>
+      <c r="B247" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q247" s="2">
+        <v>76.319600202338691</v>
+      </c>
+      <c r="R247">
+        <v>5</v>
+      </c>
+      <c r="T247">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="248" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>2024</v>
+      </c>
+      <c r="B248" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q248" s="2">
+        <v>86.603809721553674</v>
+      </c>
+      <c r="R248">
+        <v>5</v>
+      </c>
+      <c r="T248">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="249" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>2024</v>
+      </c>
+      <c r="B249" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q249" s="2">
+        <v>80.782091373165869</v>
+      </c>
+      <c r="R249">
+        <v>5</v>
+      </c>
+      <c r="T249">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="250" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>2024</v>
+      </c>
+      <c r="B250" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q250" s="2">
+        <v>82.836593854624951</v>
+      </c>
+      <c r="R250">
+        <v>5</v>
+      </c>
+      <c r="T250">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="251" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>2024</v>
+      </c>
+      <c r="B251" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q251" s="2">
+        <v>85.308800038429524</v>
+      </c>
+      <c r="R251">
+        <v>5</v>
+      </c>
+      <c r="T251">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="252" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>2024</v>
+      </c>
+      <c r="B252" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q252" s="2">
+        <v>81.090559143448885</v>
+      </c>
+      <c r="R252">
+        <v>5</v>
+      </c>
+      <c r="T252">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="253" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>2024</v>
+      </c>
+      <c r="B253" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q253" s="2">
+        <v>85.929692625094347</v>
+      </c>
+      <c r="R253">
+        <v>5</v>
+      </c>
+      <c r="T253">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="254" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>2024</v>
+      </c>
+      <c r="B254" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q254" s="2">
+        <v>82.420478291392243</v>
+      </c>
+      <c r="R254">
+        <v>5</v>
+      </c>
+      <c r="T254">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="255" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>2024</v>
+      </c>
+      <c r="B255" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q255" s="2">
+        <v>86.540012808802828</v>
+      </c>
+      <c r="R255">
+        <v>5</v>
+      </c>
+      <c r="T255">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="256" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>2024</v>
+      </c>
+      <c r="B256" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q256" s="2">
+        <v>75.195600047874464</v>
+      </c>
+      <c r="R256">
+        <v>4</v>
+      </c>
+      <c r="T256">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>2024</v>
+      </c>
+      <c r="B257" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q257" s="2">
+        <v>77.147599068949503</v>
+      </c>
+      <c r="R257">
+        <v>5</v>
+      </c>
+      <c r="T257">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="258" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>2024</v>
+      </c>
+      <c r="B258" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q258" s="2">
+        <v>77.660180828972642</v>
+      </c>
+      <c r="R258">
+        <v>5</v>
+      </c>
+      <c r="T258">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="259" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>2024</v>
+      </c>
+      <c r="B259" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q259" s="2">
+        <v>87.509463091703608</v>
+      </c>
+      <c r="R259">
+        <v>6</v>
+      </c>
+      <c r="T259">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="260" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>2024</v>
+      </c>
+      <c r="B260" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q260" s="2">
+        <v>73.016692869274465</v>
+      </c>
+      <c r="R260">
+        <v>4</v>
+      </c>
+      <c r="T260">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="261" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>2024</v>
+      </c>
+      <c r="B261" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q261" s="2">
+        <v>74.347665543219605</v>
+      </c>
+      <c r="R261">
+        <v>4</v>
+      </c>
+      <c r="T261">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="262" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>2024</v>
+      </c>
+      <c r="B262" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q262" s="2">
+        <v>87.225132371580926</v>
+      </c>
+      <c r="R262">
+        <v>6</v>
+      </c>
+      <c r="T262">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="263" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>2024</v>
+      </c>
+      <c r="B263" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q263" s="2">
+        <v>78.447544514433929</v>
+      </c>
+      <c r="R263">
+        <v>5</v>
+      </c>
+      <c r="T263">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="264" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>2024</v>
+      </c>
+      <c r="B264" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q264" s="2">
+        <v>70.899600093641283</v>
+      </c>
+      <c r="R264">
+        <v>4</v>
+      </c>
+      <c r="T264">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="265" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>2024</v>
+      </c>
+      <c r="B265" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q265" s="2">
+        <v>82.609628757184666</v>
+      </c>
+      <c r="R265">
+        <v>5</v>
+      </c>
+      <c r="T265">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="266" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>2024</v>
+      </c>
+      <c r="B266" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q266" s="2">
+        <v>84.802588799347276</v>
+      </c>
+      <c r="R266">
+        <v>5</v>
+      </c>
+      <c r="T266">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="267" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>2024</v>
+      </c>
+      <c r="B267" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q267" s="2">
+        <v>87.143581224275493</v>
+      </c>
+      <c r="R267">
+        <v>6</v>
+      </c>
+      <c r="T267">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="268" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A268">
         <v>2025</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B268" t="s">
+        <v>21</v>
+      </c>
+      <c r="C268">
+        <v>205162.25889999999</v>
+      </c>
+      <c r="D268">
+        <v>104471.6853</v>
+      </c>
+      <c r="E268">
+        <v>6876.6278000000002</v>
+      </c>
+      <c r="F268">
+        <v>21385.463599999999</v>
+      </c>
+      <c r="G268">
+        <v>42</v>
+      </c>
+      <c r="H268">
+        <v>23</v>
+      </c>
+      <c r="I268">
+        <v>263</v>
+      </c>
+      <c r="J268">
+        <v>27</v>
+      </c>
+      <c r="K268">
+        <v>902369.84510000004</v>
+      </c>
+      <c r="L268">
+        <v>66.55</v>
+      </c>
+      <c r="M268">
+        <v>2664304.0359999998</v>
+      </c>
+      <c r="N268">
+        <v>7.45</v>
+      </c>
+      <c r="O268">
+        <v>17.940000000000001</v>
+      </c>
+      <c r="P268">
+        <v>29096.117200000001</v>
+      </c>
+      <c r="Q268">
+        <v>73.59</v>
+      </c>
+      <c r="R268">
+        <v>4</v>
+      </c>
+      <c r="S268">
+        <v>4</v>
+      </c>
+      <c r="T268">
+        <v>4</v>
+      </c>
+      <c r="U268">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>2025</v>
+      </c>
+      <c r="B269" t="s">
         <v>22</v>
       </c>
-      <c r="C203">
+      <c r="C269">
         <v>490898.70110000001</v>
       </c>
-      <c r="D203">
+      <c r="D269">
         <v>245471.20610000001</v>
       </c>
-      <c r="E203">
+      <c r="E269">
         <v>25717.314699999999</v>
       </c>
-      <c r="F203">
+      <c r="F269">
         <v>10545.223900000001</v>
       </c>
-      <c r="G203">
+      <c r="G269">
         <v>98</v>
       </c>
-      <c r="H203">
+      <c r="H269">
         <v>47</v>
       </c>
-      <c r="I203">
+      <c r="I269">
         <v>133</v>
       </c>
-      <c r="J203">
+      <c r="J269">
         <v>87</v>
       </c>
-      <c r="K203">
+      <c r="K269">
         <v>1266692.9550000001</v>
       </c>
-      <c r="L203">
+      <c r="L269">
         <v>73.44</v>
       </c>
-      <c r="M203">
+      <c r="M269">
         <v>2270677.9649999999</v>
       </c>
-      <c r="N203">
+      <c r="N269">
         <v>4.66</v>
       </c>
-      <c r="O203">
+      <c r="O269">
         <v>6.01</v>
       </c>
-      <c r="P203">
+      <c r="P269">
         <v>62306.179400000001</v>
       </c>
-      <c r="Q203">
+      <c r="Q269">
         <v>86.82</v>
       </c>
-      <c r="R203">
-        <v>5</v>
-      </c>
-      <c r="S203">
-        <v>5</v>
-      </c>
-      <c r="T203">
-        <v>5</v>
-      </c>
-      <c r="U203">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="204" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A204">
+      <c r="R269">
+        <v>5</v>
+      </c>
+      <c r="S269">
+        <v>5</v>
+      </c>
+      <c r="T269">
+        <v>5</v>
+      </c>
+      <c r="U269">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="270" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A270">
         <v>2025</v>
       </c>
-      <c r="B204" t="s">
+      <c r="B270" t="s">
         <v>23</v>
       </c>
-      <c r="C204">
+      <c r="C270">
         <v>230883.80910000001</v>
       </c>
-      <c r="D204">
+      <c r="D270">
         <v>306487.48249999998</v>
       </c>
-      <c r="E204">
+      <c r="E270">
         <v>6043.5796</v>
       </c>
-      <c r="F204">
+      <c r="F270">
         <v>80875.722899999993</v>
       </c>
-      <c r="G204">
+      <c r="G270">
         <v>101</v>
       </c>
-      <c r="H204">
+      <c r="H270">
         <v>16</v>
       </c>
-      <c r="I204">
+      <c r="I270">
         <v>248</v>
       </c>
-      <c r="J204">
+      <c r="J270">
         <v>84</v>
       </c>
-      <c r="K204">
+      <c r="K270">
         <v>1094242.716</v>
       </c>
-      <c r="L204">
+      <c r="L270">
         <v>73.36</v>
       </c>
-      <c r="M204">
+      <c r="M270">
         <v>2164780.7450000001</v>
       </c>
-      <c r="N204">
+      <c r="N270">
         <v>4.8499999999999996</v>
       </c>
-      <c r="O204">
+      <c r="O270">
         <v>7.21</v>
       </c>
-      <c r="P204">
+      <c r="P270">
         <v>38531.142999999996</v>
       </c>
-      <c r="Q204">
+      <c r="Q270">
         <v>87.34</v>
       </c>
-      <c r="R204">
-        <v>6</v>
-      </c>
-      <c r="S204">
-        <v>6</v>
-      </c>
-      <c r="T204">
-        <v>6</v>
-      </c>
-      <c r="U204">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="205" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A205">
+      <c r="R270">
+        <v>6</v>
+      </c>
+      <c r="S270">
+        <v>6</v>
+      </c>
+      <c r="T270">
+        <v>6</v>
+      </c>
+      <c r="U270">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="271" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A271">
         <v>2025</v>
       </c>
-      <c r="B205" t="s">
+      <c r="B271" t="s">
         <v>24</v>
       </c>
-      <c r="C205">
+      <c r="C271">
         <v>758974.73060000001</v>
       </c>
-      <c r="D205">
+      <c r="D271">
         <v>253991.64509999999</v>
       </c>
-      <c r="E205">
+      <c r="E271">
         <v>2544.7768000000001</v>
       </c>
-      <c r="F205">
+      <c r="F271">
         <v>25410.625599999999</v>
       </c>
-      <c r="G205">
+      <c r="G271">
         <v>70</v>
       </c>
-      <c r="H205">
+      <c r="H271">
         <v>25</v>
       </c>
-      <c r="I205">
+      <c r="I271">
         <v>368</v>
       </c>
-      <c r="J205">
+      <c r="J271">
         <v>74</v>
       </c>
-      <c r="K205">
+      <c r="K271">
         <v>1067567.5630000001</v>
       </c>
-      <c r="L205">
+      <c r="L271">
         <v>71.626000000000005</v>
       </c>
-      <c r="M205">
+      <c r="M271">
         <v>2597260.5929999999</v>
       </c>
-      <c r="N205">
+      <c r="N271">
         <v>4.09</v>
       </c>
-      <c r="O205">
+      <c r="O271">
         <v>10.79</v>
       </c>
-      <c r="P205">
+      <c r="P271">
         <v>88566.705300000001</v>
       </c>
-      <c r="Q205">
+      <c r="Q271">
         <v>86.55</v>
       </c>
-      <c r="R205">
-        <v>6</v>
-      </c>
-      <c r="S205">
-        <v>6</v>
-      </c>
-      <c r="T205">
-        <v>6</v>
-      </c>
-      <c r="U205">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="206" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A206">
+      <c r="R271">
+        <v>6</v>
+      </c>
+      <c r="S271">
+        <v>6</v>
+      </c>
+      <c r="T271">
+        <v>6</v>
+      </c>
+      <c r="U271">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="272" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A272">
         <v>2025</v>
       </c>
-      <c r="B206" t="s">
+      <c r="B272" t="s">
         <v>25</v>
       </c>
-      <c r="C206">
+      <c r="C272">
         <v>261468.16070000001</v>
       </c>
-      <c r="D206">
+      <c r="D272">
         <v>223622.1378</v>
       </c>
-      <c r="E206">
+      <c r="E272">
         <v>4524.9908999999998</v>
       </c>
-      <c r="F206">
+      <c r="F272">
         <v>48723.242899999997</v>
       </c>
-      <c r="G206">
+      <c r="G272">
         <v>50</v>
       </c>
-      <c r="H206">
+      <c r="H272">
         <v>15</v>
       </c>
-      <c r="I206">
+      <c r="I272">
         <v>171</v>
       </c>
-      <c r="J206">
+      <c r="J272">
         <v>71</v>
       </c>
-      <c r="K206">
+      <c r="K272">
         <v>1064447.2679999999</v>
       </c>
-      <c r="L206">
+      <c r="L272">
         <v>68.81</v>
       </c>
-      <c r="M206">
+      <c r="M272">
         <v>1940478.4979999999</v>
       </c>
-      <c r="N206">
+      <c r="N272">
         <v>3.72</v>
       </c>
-      <c r="O206">
+      <c r="O272">
         <v>11.97</v>
       </c>
-      <c r="P206">
+      <c r="P272">
         <v>33821.843399999998</v>
       </c>
-      <c r="Q206">
+      <c r="Q272">
         <v>76.78</v>
       </c>
-      <c r="R206">
-        <v>5</v>
-      </c>
-      <c r="S206">
-        <v>5</v>
-      </c>
-      <c r="T206">
-        <v>5</v>
-      </c>
-      <c r="U206">
-        <v>5</v>
+      <c r="R272">
+        <v>5</v>
+      </c>
+      <c r="S272">
+        <v>5</v>
+      </c>
+      <c r="T272">
+        <v>5</v>
+      </c>
+      <c r="U272">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="273" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>2025</v>
+      </c>
+      <c r="B273" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q273" s="2">
+        <v>84.124857653711004</v>
+      </c>
+      <c r="R273">
+        <v>5</v>
+      </c>
+      <c r="T273">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="274" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>2025</v>
+      </c>
+      <c r="B274" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q274" s="2">
+        <v>79.319322430904009</v>
+      </c>
+      <c r="R274">
+        <v>5</v>
+      </c>
+      <c r="T274">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="275" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A275">
+        <v>2025</v>
+      </c>
+      <c r="B275" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q275" s="2">
+        <v>85.622013194893867</v>
+      </c>
+      <c r="R275">
+        <v>5</v>
+      </c>
+      <c r="T275">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="276" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A276">
+        <v>2025</v>
+      </c>
+      <c r="B276" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q276" s="2">
+        <v>76.27104007441045</v>
+      </c>
+      <c r="R276">
+        <v>5</v>
+      </c>
+      <c r="T276">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="277" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A277">
+        <v>2025</v>
+      </c>
+      <c r="B277" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q277" s="2">
+        <v>82.817803911589863</v>
+      </c>
+      <c r="R277">
+        <v>5</v>
+      </c>
+      <c r="T277">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="278" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>2025</v>
+      </c>
+      <c r="B278" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q278" s="2">
+        <v>75.753223102689446</v>
+      </c>
+      <c r="R278">
+        <v>4</v>
+      </c>
+      <c r="T278">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>2025</v>
+      </c>
+      <c r="B279" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q279" s="2">
+        <v>73.760282649692954</v>
+      </c>
+      <c r="R279">
+        <v>4</v>
+      </c>
+      <c r="T279">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>2025</v>
+      </c>
+      <c r="B280" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q280" s="2">
+        <v>85.296842260344491</v>
+      </c>
+      <c r="R280">
+        <v>5</v>
+      </c>
+      <c r="T280">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="281" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>2025</v>
+      </c>
+      <c r="B281" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q281" s="2">
+        <v>74.231739376352621</v>
+      </c>
+      <c r="R281">
+        <v>4</v>
+      </c>
+      <c r="T281">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="282" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>2025</v>
+      </c>
+      <c r="B282" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q282" s="2">
+        <v>83.134589918838984</v>
+      </c>
+      <c r="R282">
+        <v>5</v>
+      </c>
+      <c r="T282">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="283" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>2025</v>
+      </c>
+      <c r="B283" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q283" s="2">
+        <v>73.555798787814823</v>
+      </c>
+      <c r="R283">
+        <v>4</v>
+      </c>
+      <c r="T283">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="284" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>2025</v>
+      </c>
+      <c r="B284" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q284" s="2">
+        <v>75.314315885071693</v>
+      </c>
+      <c r="R284">
+        <v>4</v>
+      </c>
+      <c r="T284">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="285" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>2025</v>
+      </c>
+      <c r="B285" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q285" s="2">
+        <v>74.445680254889965</v>
+      </c>
+      <c r="R285">
+        <v>4</v>
+      </c>
+      <c r="T285">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="286" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>2025</v>
+      </c>
+      <c r="B286" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q286" s="2">
+        <v>86.714733378807807</v>
+      </c>
+      <c r="R286">
+        <v>5</v>
+      </c>
+      <c r="T286">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="287" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>2025</v>
+      </c>
+      <c r="B287" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q287" s="2">
+        <v>81.2948349705987</v>
+      </c>
+      <c r="R287">
+        <v>5</v>
+      </c>
+      <c r="T287">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="288" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>2025</v>
+      </c>
+      <c r="B288" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q288" s="2">
+        <v>82.421399348184593</v>
+      </c>
+      <c r="R288">
+        <v>5</v>
+      </c>
+      <c r="T288">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="289" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A289">
+        <v>2025</v>
+      </c>
+      <c r="B289" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q289" s="2">
+        <v>84.935040048225659</v>
+      </c>
+      <c r="R289">
+        <v>5</v>
+      </c>
+      <c r="T289">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="290" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>2025</v>
+      </c>
+      <c r="B290" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q290" s="2">
+        <v>81.32581982974898</v>
+      </c>
+      <c r="R290">
+        <v>5</v>
+      </c>
+      <c r="T290">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="291" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A291">
+        <v>2025</v>
+      </c>
+      <c r="B291" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q291" s="2">
+        <v>86.202166120595251</v>
+      </c>
+      <c r="R291">
+        <v>5</v>
+      </c>
+      <c r="T291">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="292" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A292">
+        <v>2025</v>
+      </c>
+      <c r="B292" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q292" s="2">
+        <v>82.633981679823563</v>
+      </c>
+      <c r="R292">
+        <v>5</v>
+      </c>
+      <c r="T292">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="293" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A293">
+        <v>2025</v>
+      </c>
+      <c r="B293" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q293" s="2">
+        <v>86.98994173662372</v>
+      </c>
+      <c r="R293">
+        <v>6</v>
+      </c>
+      <c r="T293">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="294" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A294">
+        <v>2025</v>
+      </c>
+      <c r="B294" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q294" s="2">
+        <v>74.294480058708217</v>
+      </c>
+      <c r="R294">
+        <v>4</v>
+      </c>
+      <c r="T294">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="295" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A295">
+        <v>2025</v>
+      </c>
+      <c r="B295" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q295" s="2">
+        <v>78.120967607347978</v>
+      </c>
+      <c r="R295">
+        <v>5</v>
+      </c>
+      <c r="T295">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="296" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A296">
+        <v>2025</v>
+      </c>
+      <c r="B296" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q296" s="2">
+        <v>77.727948698888909</v>
+      </c>
+      <c r="R296">
+        <v>5</v>
+      </c>
+      <c r="T296">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="297" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A297">
+        <v>2025</v>
+      </c>
+      <c r="B297" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q297" s="2">
+        <v>87.91330638693853</v>
+      </c>
+      <c r="R297">
+        <v>6</v>
+      </c>
+      <c r="T297">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="298" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A298">
+        <v>2025</v>
+      </c>
+      <c r="B298" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q298" s="2">
+        <v>73.658440760754559</v>
+      </c>
+      <c r="R298">
+        <v>4</v>
+      </c>
+      <c r="T298">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="299" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A299">
+        <v>2025</v>
+      </c>
+      <c r="B299" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q299" s="2">
+        <v>74.690181000606273</v>
+      </c>
+      <c r="R299">
+        <v>4</v>
+      </c>
+      <c r="T299">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="300" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A300">
+        <v>2025</v>
+      </c>
+      <c r="B300" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q300" s="2">
+        <v>87.97021354140179</v>
+      </c>
+      <c r="R300">
+        <v>6</v>
+      </c>
+      <c r="T300">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="301" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A301">
+        <v>2025</v>
+      </c>
+      <c r="B301" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q301" s="2">
+        <v>78.691878553922137</v>
+      </c>
+      <c r="R301">
+        <v>5</v>
+      </c>
+      <c r="T301">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="302" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A302">
+        <v>2025</v>
+      </c>
+      <c r="B302" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q302" s="2">
+        <v>69.793680115491867</v>
+      </c>
+      <c r="R302">
+        <v>4</v>
+      </c>
+      <c r="T302">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="303" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A303">
+        <v>2025</v>
+      </c>
+      <c r="B303" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q303" s="2">
+        <v>83.06232068818835</v>
+      </c>
+      <c r="R303">
+        <v>5</v>
+      </c>
+      <c r="T303">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="304" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A304">
+        <v>2025</v>
+      </c>
+      <c r="B304" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q304" s="2">
+        <v>85.130139550908254</v>
+      </c>
+      <c r="R304">
+        <v>5</v>
+      </c>
+      <c r="T304">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="305" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A305">
+        <v>2025</v>
+      </c>
+      <c r="B305" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q305" s="2">
+        <v>87.474070872493712</v>
+      </c>
+      <c r="R305">
+        <v>6</v>
+      </c>
+      <c r="T305">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
